--- a/db/tabla_unique_38.xlsx
+++ b/db/tabla_unique_38.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminserranobarba/Desktop/Trabajo/web-app/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminserranobarba/Desktop/Trabajo/web-app/estadia-back/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C4213A-DD7A-F24F-B906-B5ACAFCA554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5500080D-1A25-7A4E-8377-2D458724749D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,9 +622,6 @@
     <t>KO_code</t>
   </si>
   <si>
-    <t>Protein.accession</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -643,9 +640,6 @@
     <t>End</t>
   </si>
   <si>
-    <t>Protein.length</t>
-  </si>
-  <si>
     <t>Orientation</t>
   </si>
   <si>
@@ -704,6 +698,12 @@
   </si>
   <si>
     <t>Genetic Information Processing</t>
+  </si>
+  <si>
+    <t>Protein_accession</t>
+  </si>
+  <si>
+    <t>Protein_length</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2040,7 @@
     <row r="1" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>0</v>
@@ -2049,55 +2049,55 @@
         <v>198</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>197</v>
       </c>
       <c r="H1" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="O1" s="14" t="s">
         <v>190</v>
       </c>
       <c r="P1" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="R1" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -2150,19 +2150,19 @@
         <v>191</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="S2" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
@@ -2264,7 +2264,7 @@
         <v>191</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
@@ -2318,10 +2318,10 @@
         <v>191</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
@@ -2422,10 +2422,10 @@
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
@@ -2477,10 +2477,10 @@
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
@@ -2635,7 +2635,7 @@
         <v>191</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -2692,7 +2692,7 @@
         <v>191</v>
       </c>
       <c r="Q12" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
@@ -2749,7 +2749,7 @@
         <v>191</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
@@ -2801,10 +2801,10 @@
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
@@ -2861,7 +2861,7 @@
         <v>191</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
@@ -3016,7 +3016,7 @@
         <v>191</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
@@ -3073,7 +3073,7 @@
         <v>191</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
@@ -3125,10 +3125,10 @@
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q20" s="13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
@@ -3182,10 +3182,10 @@
         <v>192</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q21" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
@@ -3242,13 +3242,13 @@
         <v>191</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
@@ -3300,10 +3300,10 @@
         <v>191</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q23" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
@@ -3357,10 +3357,10 @@
         <v>196</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q24" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
@@ -3412,10 +3412,10 @@
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q25" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
@@ -3467,10 +3467,10 @@
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
@@ -3524,10 +3524,10 @@
         <v>196</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
@@ -3579,10 +3579,10 @@
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
@@ -3634,10 +3634,10 @@
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
@@ -3692,7 +3692,7 @@
         <v>191</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
@@ -3891,10 +3891,10 @@
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q34" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
@@ -3995,10 +3995,10 @@
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q36" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -4120,7 +4120,7 @@
         <v>160</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G39" s="10">
         <v>-112805041600968</v>
@@ -4153,7 +4153,7 @@
         <v>191</v>
       </c>
       <c r="Q39" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
@@ -4256,10 +4256,10 @@
         <v>192</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q41" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
@@ -4316,7 +4316,7 @@
         <v>191</v>
       </c>
       <c r="Q42" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
@@ -4417,10 +4417,10 @@
       </c>
       <c r="O44" s="2"/>
       <c r="P44" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q44" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
